--- a/data/trans_dic/IP22_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP22_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,53; 22,04</t>
+          <t>10,96; 22,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 32,13</t>
+          <t>18,09; 32,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,29; 27,43</t>
+          <t>13,82; 27,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,84; 26,93</t>
+          <t>14,83; 27,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 29,63</t>
+          <t>16,22; 29,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,14; 32,31</t>
+          <t>17,52; 33,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,64; 26,31</t>
+          <t>13,71; 26,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,07; 20,53</t>
+          <t>10,06; 20,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,8; 23,93</t>
+          <t>15,25; 23,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,5; 29,73</t>
+          <t>19,33; 30,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,13; 24,5</t>
+          <t>14,94; 24,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,64; 22,04</t>
+          <t>13,37; 21,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,85; 34,09</t>
+          <t>18,55; 32,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,42; 32,98</t>
+          <t>18,18; 32,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,14; 23,74</t>
+          <t>12,41; 25,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 18,13</t>
+          <t>7,39; 17,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 32,29</t>
+          <t>17,14; 32,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,7; 36,26</t>
+          <t>20,76; 36,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 21,91</t>
+          <t>10,91; 22,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 23,16</t>
+          <t>9,08; 21,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 30,41</t>
+          <t>20,12; 30,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,88; 32,7</t>
+          <t>21,82; 32,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 21,0</t>
+          <t>13,02; 21,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 18,18</t>
+          <t>9,24; 18,31</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,21; 33,04</t>
+          <t>15,89; 32,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,11; 27,89</t>
+          <t>13,55; 27,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 21,23</t>
+          <t>7,6; 22,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 24,78</t>
+          <t>7,37; 23,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,86; 31,43</t>
+          <t>17,49; 31,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,19; 30,87</t>
+          <t>16,37; 32,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 26,59</t>
+          <t>12,67; 27,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 33,49</t>
+          <t>13,37; 32,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 29,05</t>
+          <t>18,81; 29,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,71; 26,97</t>
+          <t>16,76; 26,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,1; 22,03</t>
+          <t>11,73; 22,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,31; 26,25</t>
+          <t>12,71; 26,81</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,54; 25,86</t>
+          <t>16,61; 25,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,26; 33,51</t>
+          <t>23,42; 33,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,22; 23,87</t>
+          <t>15,74; 24,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 24,46</t>
+          <t>11,04; 25,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 27,52</t>
+          <t>17,88; 27,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,69; 34,54</t>
+          <t>24,44; 34,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,03; 21,45</t>
+          <t>12,38; 21,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,57; 22,24</t>
+          <t>12,59; 22,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,22; 24,81</t>
+          <t>18,48; 24,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,77; 32,95</t>
+          <t>25,36; 32,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,58; 21,42</t>
+          <t>15,18; 21,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,62; 21,34</t>
+          <t>12,87; 21,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 21,49</t>
+          <t>9,69; 21,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,36; 26,3</t>
+          <t>15,52; 26,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,88; 24,65</t>
+          <t>14,18; 24,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,55; 22,11</t>
+          <t>11,05; 22,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,86; 26,29</t>
+          <t>15,16; 26,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,14; 37,72</t>
+          <t>24,99; 38,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,85; 24,41</t>
+          <t>12,56; 23,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,0; 22,0</t>
+          <t>9,9; 21,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,42; 22,75</t>
+          <t>14,21; 22,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,17; 30,11</t>
+          <t>21,35; 30,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,95; 22,37</t>
+          <t>14,88; 22,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,61; 19,68</t>
+          <t>11,59; 19,93</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,94; 29,94</t>
+          <t>13,71; 29,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,73; 23,64</t>
+          <t>6,67; 23,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 18,19</t>
+          <t>5,28; 18,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,83; 16,78</t>
+          <t>4,32; 17,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 26,26</t>
+          <t>11,23; 25,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,19; 32,41</t>
+          <t>15,59; 32,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,63; 21,71</t>
+          <t>7,56; 22,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 16,17</t>
+          <t>4,01; 15,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,71; 25,4</t>
+          <t>14,15; 25,13</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,1; 25,45</t>
+          <t>14,2; 26,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,85; 17,4</t>
+          <t>7,78; 17,35</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,91; 13,66</t>
+          <t>5,09; 13,8</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,41; 22,4</t>
+          <t>17,44; 22,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,73; 26,36</t>
+          <t>20,76; 26,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,54; 20,15</t>
+          <t>15,4; 19,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,69; 18,86</t>
+          <t>12,96; 19,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,41; 24,55</t>
+          <t>19,7; 24,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,77; 30,27</t>
+          <t>24,66; 30,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,9; 19,63</t>
+          <t>14,69; 19,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,1</t>
+          <t>12,86; 17,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,27; 22,92</t>
+          <t>19,39; 23,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,68; 27,56</t>
+          <t>23,69; 27,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,87; 19,17</t>
+          <t>15,6; 18,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,52; 17,61</t>
+          <t>13,61; 17,44</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10984; 22998</t>
+          <t>11442; 23131</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15549; 28891</t>
+          <t>16271; 29027</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11041; 22792</t>
+          <t>11484; 22962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15501; 28134</t>
+          <t>15491; 28536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15648; 28907</t>
+          <t>15822; 28924</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15386; 29005</t>
+          <t>15723; 30019</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12513; 26044</t>
+          <t>13574; 26517</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13786; 28101</t>
+          <t>13780; 28183</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29878; 48311</t>
+          <t>30780; 48045</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35032; 53419</t>
+          <t>34740; 54062</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27540; 44616</t>
+          <t>27205; 43915</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32934; 53201</t>
+          <t>32278; 52850</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16469; 29788</t>
+          <t>16214; 28746</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17180; 30757</t>
+          <t>16952; 30626</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12839; 25101</t>
+          <t>13117; 26486</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6748; 17036</t>
+          <t>6946; 16801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14816; 27762</t>
+          <t>14737; 27968</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19877; 34826</t>
+          <t>19941; 34767</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12476; 24699</t>
+          <t>12302; 24854</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8835; 22133</t>
+          <t>8677; 20961</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34177; 52716</t>
+          <t>34883; 52682</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41427; 61901</t>
+          <t>41310; 61331</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27935; 45881</t>
+          <t>28452; 46331</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17566; 34463</t>
+          <t>17510; 34702</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10923; 22264</t>
+          <t>10709; 21786</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12157; 24026</t>
+          <t>11670; 23893</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4900; 13131</t>
+          <t>4700; 13668</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4406; 12850</t>
+          <t>3821; 12349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16749; 31218</t>
+          <t>17372; 30845</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14065; 26822</t>
+          <t>14225; 27818</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9450; 20059</t>
+          <t>9559; 21080</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8555; 21382</t>
+          <t>8535; 20798</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31131; 48433</t>
+          <t>31356; 48435</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28910; 46667</t>
+          <t>29004; 46595</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16607; 30233</t>
+          <t>16104; 30270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14245; 30379</t>
+          <t>14709; 31018</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33198; 51903</t>
+          <t>33334; 51771</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47934; 69066</t>
+          <t>48276; 69389</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34032; 53361</t>
+          <t>35185; 53866</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22692; 53335</t>
+          <t>24070; 55296</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35972; 55616</t>
+          <t>36139; 54939</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56155; 78549</t>
+          <t>55591; 77796</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27472; 45218</t>
+          <t>26107; 44324</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27439; 48543</t>
+          <t>27487; 48436</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73397; 99934</t>
+          <t>74453; 100056</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111741; 142868</t>
+          <t>109967; 141466</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67683; 93045</t>
+          <t>65957; 92618</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>55058; 93093</t>
+          <t>56147; 94879</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10255; 22379</t>
+          <t>10088; 22020</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22916; 39229</t>
+          <t>23149; 39702</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18906; 33566</t>
+          <t>19318; 33522</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13795; 26407</t>
+          <t>13196; 26440</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18911; 33465</t>
+          <t>19297; 33728</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33834; 52875</t>
+          <t>35033; 53500</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18388; 34921</t>
+          <t>17974; 33402</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16266; 35770</t>
+          <t>16106; 34709</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33373; 52653</t>
+          <t>32887; 51608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61263; 87121</t>
+          <t>61763; 87400</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41764; 62465</t>
+          <t>41562; 63162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32732; 55514</t>
+          <t>32693; 56208</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10440; 22414</t>
+          <t>10267; 22188</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3627; 12743</t>
+          <t>3597; 12684</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2883; 11110</t>
+          <t>3228; 11461</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2638; 11559</t>
+          <t>2975; 12141</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8027; 19008</t>
+          <t>8129; 18709</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11986; 23997</t>
+          <t>11543; 23993</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5173; 14728</t>
+          <t>5127; 15195</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2685; 11644</t>
+          <t>2888; 11121</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21667; 37401</t>
+          <t>20832; 37014</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18045; 32560</t>
+          <t>18170; 33403</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10120; 22427</t>
+          <t>10036; 22372</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6923; 19253</t>
+          <t>7167; 19441</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>111208; 143092</t>
+          <t>111410; 146150</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140641; 178897</t>
+          <t>140889; 177478</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104381; 135328</t>
+          <t>103436; 134118</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83342; 123822</t>
+          <t>85124; 125224</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>132895; 168055</t>
+          <t>134834; 167885</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>176958; 216198</t>
+          <t>176150; 217400</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>105612; 139176</t>
+          <t>104153; 139689</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>97066; 135642</t>
+          <t>96330; 134459</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>254998; 303286</t>
+          <t>256665; 304374</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>329834; 383899</t>
+          <t>329946; 383079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>219026; 264577</t>
+          <t>215393; 261190</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>190028; 247636</t>
+          <t>191366; 245157</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP22_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP22_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24,36%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,1%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14,92%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15,82%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>24,43%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19,81%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,96; 22,17</t>
+          <t>16,22; 29,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,09; 32,28</t>
+          <t>17,43; 31,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,82; 27,63</t>
+          <t>13,35; 25,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,83; 27,32</t>
+          <t>9,82; 20,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,22; 29,65</t>
+          <t>11,13; 22,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,52; 33,44</t>
+          <t>18,02; 32,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,71; 26,79</t>
+          <t>13,59; 27,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,06; 20,59</t>
+          <t>14,45; 28,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,25; 23,8</t>
+          <t>15,03; 23,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,33; 30,09</t>
+          <t>19,28; 30,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 24,12</t>
+          <t>14,95; 23,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,37; 21,9</t>
+          <t>13,89; 22,41</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24,26%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>25,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>24,94%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>17,42%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,89%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,55; 32,89</t>
+          <t>17,56; 32,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 32,84</t>
+          <t>21,16; 36,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 25,05</t>
+          <t>11,02; 22,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,39; 17,88</t>
+          <t>9,26; 23,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,14; 32,53</t>
+          <t>18,57; 33,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,76; 36,2</t>
+          <t>18,61; 33,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,91; 22,04</t>
+          <t>12,03; 23,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 21,93</t>
+          <t>7,21; 17,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,12; 30,39</t>
+          <t>19,48; 30,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,82; 32,4</t>
+          <t>22,18; 33,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,02; 21,21</t>
+          <t>12,79; 20,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 18,31</t>
+          <t>9,3; 18,25</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23,77%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23,11%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21,09%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>23,21%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19,93%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>13,66%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,89; 32,33</t>
+          <t>17,71; 30,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,55; 27,73</t>
+          <t>16,41; 31,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 22,1</t>
+          <t>12,29; 27,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 23,81</t>
+          <t>11,88; 32,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,49; 31,05</t>
+          <t>15,5; 32,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,37; 32,01</t>
+          <t>13,48; 27,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,67; 27,95</t>
+          <t>7,19; 20,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,37; 32,57</t>
+          <t>8,05; 22,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,81; 29,05</t>
+          <t>18,47; 29,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 26,93</t>
+          <t>17,02; 27,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,73; 22,05</t>
+          <t>12,27; 22,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,71; 26,81</t>
+          <t>12,02; 24,46</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29,47%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>20,83%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>28,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19,61%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 25,79</t>
+          <t>17,88; 27,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,42; 33,67</t>
+          <t>24,9; 34,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 24,09</t>
+          <t>12,34; 21,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 25,36</t>
+          <t>11,53; 20,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,88; 27,19</t>
+          <t>16,71; 25,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,44; 34,21</t>
+          <t>23,33; 34,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 21,02</t>
+          <t>15,5; 24,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,59; 22,19</t>
+          <t>12,23; 21,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,48; 24,84</t>
+          <t>18,45; 25,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,36; 32,63</t>
+          <t>25,76; 32,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,18; 21,32</t>
+          <t>15,32; 21,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,87; 21,75</t>
+          <t>13,19; 19,85</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>20,34%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30,53%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>15,03%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,63%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,93%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 21,15</t>
+          <t>14,84; 25,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,52; 26,62</t>
+          <t>24,3; 37,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,18; 24,61</t>
+          <t>12,71; 24,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 22,14</t>
+          <t>9,82; 21,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,16; 26,5</t>
+          <t>10,05; 21,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,99; 38,17</t>
+          <t>14,96; 25,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,56; 23,34</t>
+          <t>14,05; 24,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,9; 21,34</t>
+          <t>10,81; 22,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,21; 22,3</t>
+          <t>14,15; 22,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,35; 30,21</t>
+          <t>21,22; 29,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,88; 22,62</t>
+          <t>14,94; 22,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 19,93</t>
+          <t>11,78; 20,09</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17,83%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23,39%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20,82%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>13,66%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>10,29%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,83%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,71; 29,64</t>
+          <t>11,77; 26,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,67; 23,53</t>
+          <t>15,61; 31,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,28; 18,76</t>
+          <t>7,82; 21,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,32; 17,62</t>
+          <t>3,86; 17,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 25,84</t>
+          <t>13,79; 29,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,59; 32,41</t>
+          <t>6,97; 23,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 22,4</t>
+          <t>5,08; 18,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,01; 15,45</t>
+          <t>4,45; 18,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,15; 25,13</t>
+          <t>14,59; 25,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,2; 26,11</t>
+          <t>13,92; 25,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,78; 17,35</t>
+          <t>7,92; 17,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,09; 13,8</t>
+          <t>5,02; 14,25</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27,51%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17,08%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15,12%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>19,93%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>23,46%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>17,76%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,44; 22,88</t>
+          <t>19,77; 24,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,76; 26,16</t>
+          <t>24,68; 30,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,4; 19,97</t>
+          <t>15,07; 19,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,96; 19,07</t>
+          <t>12,49; 17,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,7; 24,52</t>
+          <t>17,52; 22,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,66; 30,43</t>
+          <t>20,94; 26,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,69; 19,7</t>
+          <t>15,56; 20,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,86; 17,95</t>
+          <t>12,96; 17,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,39; 23,0</t>
+          <t>19,18; 22,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,69; 27,5</t>
+          <t>23,59; 27,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,6; 18,92</t>
+          <t>15,78; 19,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,61; 17,44</t>
+          <t>13,51; 16,87</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21846</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21865</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18908</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18288</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>16510</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>21974</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>16456</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21490</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21846</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21865</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18908</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41947</t>
+          <t>39537</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11442; 23131</t>
+          <t>15824; 29178</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16271; 29027</t>
+          <t>15646; 28041</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11484; 22962</t>
+          <t>13211; 25586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15491; 28536</t>
+          <t>12035; 25148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15822; 28924</t>
+          <t>11614; 23209</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15723; 30019</t>
+          <t>16203; 29535</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13574; 26517</t>
+          <t>11296; 22883</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13780; 28183</t>
+          <t>14877; 28975</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30780; 48045</t>
+          <t>30337; 48390</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34740; 54062</t>
+          <t>34637; 54927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27205; 43915</t>
+          <t>27218; 43650</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32278; 52850</t>
+          <t>31313; 50535</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20857</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27461</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17913</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13456</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>22096</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>23265</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18414</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10971</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20857</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27461</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17913</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>24685</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16214; 28746</t>
+          <t>15094; 27824</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16952; 30626</t>
+          <t>20319; 35389</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13117; 26486</t>
+          <t>12421; 25314</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6946; 16801</t>
+          <t>8467; 21161</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14737; 27968</t>
+          <t>16224; 29057</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19941; 34767</t>
+          <t>17357; 30875</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12302; 24854</t>
+          <t>12713; 24797</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8677; 20961</t>
+          <t>6913; 17200</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34883; 52682</t>
+          <t>33765; 53182</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41310; 61331</t>
+          <t>41979; 62820</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28452; 46331</t>
+          <t>27946; 45777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17510; 34702</t>
+          <t>17406; 34170</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23611</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20079</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14466</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12007</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>15645</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>17175</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>8445</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7613</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23611</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20079</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14466</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>19371</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10709; 21786</t>
+          <t>17587; 30779</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11670; 23893</t>
+          <t>14255; 26970</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4700; 13668</t>
+          <t>9271; 20621</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3821; 12349</t>
+          <t>6767; 18684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17372; 30845</t>
+          <t>10445; 21581</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14225; 27818</t>
+          <t>11611; 23841</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9559; 21080</t>
+          <t>4449; 12931</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8535; 20798</t>
+          <t>4307; 11980</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31356; 48435</t>
+          <t>30787; 49116</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29004; 46595</t>
+          <t>29450; 47221</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16104; 30270</t>
+          <t>16846; 30948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14709; 31018</t>
+          <t>13270; 27011</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45264</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>67034</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34873</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31982</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>41819</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>58608</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>43854</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37032</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>45264</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67034</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34873</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>29367</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73487</t>
+          <t>61348</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33334; 51771</t>
+          <t>36128; 54924</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48276; 69389</t>
+          <t>56635; 78543</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35185; 53866</t>
+          <t>26018; 44643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24070; 55296</t>
+          <t>23282; 42368</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36139; 54939</t>
+          <t>33533; 51324</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55591; 77796</t>
+          <t>48077; 70145</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26107; 44324</t>
+          <t>34664; 53942</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27487; 48436</t>
+          <t>21873; 39297</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74453; 100056</t>
+          <t>74319; 102411</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>109967; 141466</t>
+          <t>111700; 141786</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65957; 92618</t>
+          <t>66549; 91264</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56147; 94879</t>
+          <t>50237; 75599</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25896</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>42789</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25559</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22750</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>15654</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>30774</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>25788</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>19099</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25896</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>42789</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>25559</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>41705</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10088; 22020</t>
+          <t>18893; 33048</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23149; 39702</t>
+          <t>34056; 52097</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19318; 33522</t>
+          <t>18184; 34695</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13196; 26440</t>
+          <t>14557; 32266</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19297; 33728</t>
+          <t>10466; 22282</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35033; 53500</t>
+          <t>22323; 38748</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17974; 33402</t>
+          <t>19138; 33734</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16106; 34709</t>
+          <t>12839; 26810</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32887; 51608</t>
+          <t>32747; 52964</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61763; 87400</t>
+          <t>61408; 86611</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41562; 63162</t>
+          <t>41735; 62777</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32693; 56208</t>
+          <t>31451; 53639</t>
         </is>
       </c>
     </row>
@@ -2831,37 +2831,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12910</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>17319</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9386</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5745</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>15590</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>7363</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>6285</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6292</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>12910</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>17319</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9386</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>12603</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10267; 22188</t>
+          <t>8521; 19164</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3597; 12684</t>
+          <t>11560; 23410</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3228; 11461</t>
+          <t>5305; 14765</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2975; 12141</t>
+          <t>2633; 11627</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8129; 18709</t>
+          <t>10327; 22136</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11543; 23993</t>
+          <t>3758; 12643</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5127; 15195</t>
+          <t>3102; 11179</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2888; 11121</t>
+          <t>3129; 13300</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20832; 37014</t>
+          <t>21485; 37236</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18170; 33403</t>
+          <t>17808; 32845</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10036; 22372</t>
+          <t>10211; 22958</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7167; 19441</t>
+          <t>6955; 19752</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>187</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>148</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>150385</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>196547</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>121105</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>104228</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>127312</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>159158</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>119242</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>102496</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>150385</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>196547</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>121105</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>115242</t>
+          <t>95021</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>217738</t>
+          <t>199249</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>111410; 146150</t>
+          <t>135318; 169058</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140889; 177478</t>
+          <t>176290; 216445</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103436; 134118</t>
+          <t>106847; 139875</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85124; 125224</t>
+          <t>86075; 123066</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>134834; 167885</t>
+          <t>111959; 143829</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>176150; 217400</t>
+          <t>142096; 176643</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>104153; 139689</t>
+          <t>104483; 137021</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>96330; 134459</t>
+          <t>80360; 111255</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>256665; 304374</t>
+          <t>253822; 300846</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>329946; 383079</t>
+          <t>328568; 384430</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>215393; 261190</t>
+          <t>217839; 262598</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>191366; 245157</t>
+          <t>176972; 220859</t>
         </is>
       </c>
     </row>
